--- a/spreadsheets/preprocessed_data.xlsx
+++ b/spreadsheets/preprocessed_data.xlsx
@@ -1,37 +1,141 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/62ecdf671660726d/Documents/MSU/Spring 2026/Data mining/Project/spreadsheets/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_0DE51DB6D16C100E62355476585DCE3A87473D1E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4C476F76-FEB9-4A0C-A217-082973423749}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Cast</t>
+  </si>
+  <si>
+    <t>Genre</t>
+  </si>
+  <si>
+    <t>Plot</t>
+  </si>
+  <si>
+    <t>Release Date</t>
+  </si>
+  <si>
+    <t>Slug</t>
+  </si>
+  <si>
+    <t>Poster Filename</t>
+  </si>
+  <si>
+    <t>Processed_Plot</t>
+  </si>
+  <si>
+    <t>Pre_director</t>
+  </si>
+  <si>
+    <t>Pre_cast</t>
+  </si>
+  <si>
+    <t>102 Dalmatians</t>
+  </si>
+  <si>
+    <t>Kevin Lima</t>
+  </si>
+  <si>
+    <t>Glenn Close, Ioan Gruffudd, Alice Evans, Tim McInnerny, Gérard Depardieu</t>
+  </si>
+  <si>
+    <t>After three years in prison following the events of the previous film , Cruella de Vil has been cured of her desire for fur coats by psychologist Dr. Pavlov and become a changed woman. She is released on probation but warned that if she breaks parole she will be immediately sent back to prison, as well as be forced to pay the remainder of her fortune, £ 8 million, to all the dog shelters in Westminster . Cruella mends her working relationship with her much-abused valet Alonzo and buys the Second Chance Dog shelter, owned by Kevin Shepherd, to save it from insolvency. Cruella's probation officer, Chloe Simon, is the owner of Dipstick (one of the original 101 Dalmatians Cruella had stolen); she suspects Cruella will strike again despite her growing popularity as an animal person. Dipstick's mate, Dottie, gives birth to three puppies: Domino, Little Dipper, and Oddball, who appears to be an albino , and begins to feel self-conscious about her lack of spots as she grows up. Meanwhile, Dr. Pavlov discovers that when his therapy patients are subjected to the chimes of Big Ben , they revert to their former personalities, but he conceals these findings from the public. Inevitably, when Big Ben rings in her presence, Cruella reverts to her former personality. After recognizing Dipstick and remembering her failed attempt of making a dalmatian fur coat, she enlists the help of French furrier Jean-Pierre LePelt. Together, they design a new fur coat, with the intention of using Dipstick's children for a hood as a part of Cruella's revenge. Chloe and Kevin go out on a date, where Kevin tells Chloe that, if Cruella violates her parole, her entire fortune will go to him, since his dog shelter is the only one currently operating in Westminster. Knowing this, Cruella has Kevin framed for the theft of the first 99 dalmatian puppies LePelt takes, also exploiting the fact that Kevin has a prior record of dog-napping. She invites Chloe and Dipstick to her house for a dinner party to decoy them away while LePelt steals Dottie and her three puppies. Dipstick quickly returns to the apartment but is later captured. Chloe rushes home to save her pets but arrives too late. She is joined by Kevin, who has escaped from prison with the help of his talking macaw , Waddlesworth. Kevin explains that his earlier conviction was for breaking animals out of a lab, where they were being used for experiments . Upon finding LePelt's lost ticket for the Venice Simplon-Orient-Express to Paris , Kevin and Chloe attempt but fail to stop Cruella and LePelt before their train departs. Waddlesworth and Oddball, who managed to escape, secretly follow them to LePelt's factory in Paris. Kevin and Chloe get there as well but they are discovered by Cruella, who locks them in a cellar. Despite this, they free the puppies through a hole in the ceiling. Cruella goes after the puppies alone, while Alonzo, having been mistreated beyond his patience, defeats LePelt and frees Kevin and Chloe. They pursue Cruella to a bakery and find that the puppies, led by Oddball, have tricked Cruella into being baked in an enormous cake. Cruella survives, then she and LePelt are both arrested. Chloe and Kevin, exonerated from the theft accusation, return to London and are personally awarded the remnants of Cruella's fortune by Alonzo himself. Oddball's coat finally develops a few small spots, much to everyone's surprise.</t>
+  </si>
+  <si>
+    <t>November 13, 2000 ( 2000-11-13 ) ( Radio City Music Hall ) November 22, 2000 ( 2000-11-22 ) (United States)</t>
+  </si>
+  <si>
+    <t>tt0211181</t>
+  </si>
+  <si>
+    <t>102_dalmatians_poster.jpg</t>
+  </si>
+  <si>
+    <t>three year prison follow event previou film cruella de vil cure desir fur coat psychologist dr pavlov becom chang woman releas probat warn break parol immedi sent back prison well forc pay remaind fortun 8 million dog shelter westminst cruella mend work relationship muchabus valet alonzo buy second chanc dog shelter own kevin shepherd save insolv cruella probat offic chloe simon owner dipstick one origin 101 dalmatian cruella stolen suspect cruella strike despit grow popular anim person dipstick mate dotti give birth three puppi domino littl dipper oddbal appear albino begin feel selfconsci lack spot grow meanwhil dr pavlov discov therapi patient subject chime big ben revert former person conceal find public inevit big ben ring presenc cruella revert former person recogn dipstick rememb fail attempt make dalmatian fur coat enlist help french furrier jeanpierr lepelt togeth design new fur coat intent use dipstick child hood part cruella reveng chloe kevin go date kevin tell chloe cruella violat parol entir fortun go sinc dog shelter one current oper westminst know cruella kevin frame theft first 99 dalmatian puppi lepelt take also exploit fact kevin prior record dognap invit chloe dipstick hous dinner parti decoy away lepelt steal dotti three puppi dipstick quickli return apart later captur chloe rush home save pet arriv late join kevin escap prison help talk macaw waddlesworth kevin explain earlier convict break anim lab use experi upon find lepelt lost ticket venic simplonorientexpress pari kevin chloe attempt fail stop cruella lepelt train depart waddlesworth oddbal manag escap secretli follow lepelt factori pari kevin chloe get well discov cruella lock cellar despit free puppi hole ceil cruella goe puppi alon alonzo mistreat beyond patienc defeat lepelt free kevin chloe pursu cruella bakeri find puppi led oddbal trick cruella bake enorm cake cruella surviv lepelt arrest chloe kevin exoner theft accus return london person award remnant cruella fortun alonzo oddbal coat final develop small spot much everyon surpris</t>
+  </si>
+  <si>
+    <t>kevin lima</t>
+  </si>
+  <si>
+    <t>['glenn close', 'ioan gruffudd', 'alice evans', 'tim mcinnerny', 'gérard depardieu']</t>
+  </si>
+  <si>
+    <t>101 Dalmatians(1996 film)</t>
+  </si>
+  <si>
+    <t>Stephen Herek</t>
+  </si>
+  <si>
+    <t>Glenn Close, Jeff Daniels, Joely Richardson, Joan Plowright</t>
+  </si>
+  <si>
+    <t>American video game designer Roger Dearly lives with his pet Dalmatian Pongo in London. Roger develops a video game featuring dog chase, but it is rejected because the villain is inadequate. His attempts to redesign the game prove unsatisfactory. One day during a walk, Pongo sets his eyes on Perdita, another Dalmatian. After a chase that ends in St James's Park , Roger discovers that Pongo likes Perdita. Her owner, Anita Campbell-Green, falls in love with Roger when they meet. When they return to Roger's home, Anita accepts his proposal. They get married along with Perdita and Pongo. Anita works as a fashion designer at the House of de Vil. Her boss, Cruella de Vil , has a deep passion for fur, going so far as to have a taxidermist , Mr. Skinner, skin a white tiger at the London Zoo to make her into a rug for her. Anita, inspired by her Dalmatian, designs a coat made with spotted fur. Cruella is intrigued by the idea of making garments out of actual Dalmatians, and finds it amusing that it would seem as if she was wearing Anita's dog. Perdita gets pregnant, and so does Anita. Cruella visits their home and becomes excited when she learns that Perdita is expecting. Weeks later, she returns when a litter of 15 puppies are born and offers Roger and Anita £7,500 for them, but they refuse. Enraged, Cruella dismisses Anita and vows revenge against her and Roger. One winter evening, she has her henchmen, Jasper and Horace, break into their home and steal the puppies, while the couple is walking in the park with Pongo and Perdita. Along with 84 other Dalmatians that were previously stolen, they deliver them to her broken-down country estate , De Vil Mansion. Cruella asks Skinner to kill and skin them to create her coat. With the family devastated at the loss of their puppies, Pongo uses the twilight bark to carry the message via the dogs and other animals of the United Kingdom, while Roger and Anita notify the police . Anita realizes Cruella was behind the kidnappings and confirms her suspicion when she shows Roger and Nanny her portfolio. An Airedale Terrier named Kipper follows Jasper and Horace to the mansion, and finds all of the puppies, who he helps escape under the duo's noses. They make their way to a nearby farm, where they are later joined by Pongo and Perdita. Cruella arrives at the mansion and discovers what has happened. Angry with the thieves' failure, she decides to carry out the job herself. After several mishaps, Jasper and Horace discover nearby police looking for Cruella and hand themselves in, joining Skinner who was attacked in defense while trying to capture a puppy who had been left behind. Cruella tracks the puppies to the farm and tries to capture them, but the farm animals incapacitate her. The police arrive and arrest Cruella, before sending the puppies home. Pongo, Perdita and their puppies are reunited with Roger, Anita and Nanny. After being informed that the remaining 84 puppies have no home to go to, as they have not yet been claimed by any owners, they decide to adopt them. Roger finally creates a successful redesign his video game, featuring Dalmatian puppies as the protagonists and Cruella as the villain. With this success, they move out of London to the countryside with their millions. Roger and Anita have a baby girl, while the dogs grow up with puppies of their own.</t>
+  </si>
+  <si>
+    <t>November 18, 1996 ( 1996-11-18 ) ( Radio City Music Hall ) November 27, 1996 ( 1996-11-27 ) (United States)</t>
+  </si>
+  <si>
+    <t>tt0115433</t>
+  </si>
+  <si>
+    <t>One_hundred_and_one_dalmatians_ver2.jpg</t>
+  </si>
+  <si>
+    <t>american video game design roger dearli live pet dalmatian pongo london roger develop video game featur dog chase reject villain inadequ attempt redesign game prove unsatisfactori one day walk pongo set eye perdita anoth dalmatian chase end st james park roger discov pongo like perdita owner anita campbellgreen fall love roger meet return roger home anita accept propos get marri along perdita pongo anita work fashion design hous de vil bos cruella de vil deep passion fur go far taxidermist mr skinner skin white tiger london zoo make rug anita inspir dalmatian design coat made spot fur cruella intrigu idea make garment actual dalmatian find amus would seem wear anita dog perdita get pregnant anita cruella visit home becom excit learn perdita expect week later return litter 15 puppi born offer roger anita 7500 refus enrag cruella dismiss anita vow reveng roger one winter even henchman jasper horac break home steal puppi coupl walk park pongo perdita along 84 dalmatian previous stolen deliv brokendown countri estat de vil mansion cruella ask skinner kill skin creat coat famili devast loss puppi pongo use twilight bark carri messag via dog anim unit kingdom roger anita notifi polic anita realiz cruella behind kidnap confirm suspicion show roger nanni portfolio airedal terrier name kipper follow jasper horac mansion find puppi help escap duo nose make way nearbi farm later join pongo perdita cruella arriv mansion discov happen angri thiev failur decid carri job sever mishap jasper horac discov nearbi polic look cruella hand join skinner attack defens tri captur puppi left behind cruella track puppi farm tri captur farm anim incapacit polic arriv arrest cruella send puppi home pongo perdita puppi reunit roger anita nanni inform remain 84 puppi home go yet claim owner decid adopt roger final creat success redesign video game featur dalmatian puppi protagonist cruella villain success move london countrysid million roger anita babi girl dog grow puppi</t>
+  </si>
+  <si>
+    <t>stephen herek</t>
+  </si>
+  <si>
+    <t>['glenn close', 'jeff daniels', 'joely richardson', 'joan plowright']</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -46,93 +150,43 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,175 +474,110 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="9" max="9" width="29.88671875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Title</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Director</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Cast</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Genre</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Plot</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Release Date</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Slug</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Poster Filename</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Processed_Plot</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Pre_director</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Pre_cast</t>
-        </is>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>102 Dalmatians</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Kevin Lima</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Glenn Close, Ioan Gruffudd, Alice Evans, Tim McInnerny, Gérard Depardieu</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>After three years in prison following the events of the previous film , Cruella de Vil has been cured of her desire for fur coats by psychologist Dr. Pavlov and become a changed woman. She is released on probation but warned that if she breaks parole she will be immediately sent back to prison, as well as be forced to pay the remainder of her fortune, £ 8 million, to all the dog shelters in Westminster . Cruella mends her working relationship with her much-abused valet Alonzo and buys the Second Chance Dog shelter, owned by Kevin Shepherd, to save it from insolvency. Cruella's probation officer, Chloe Simon, is the owner of Dipstick (one of the original 101 Dalmatians Cruella had stolen); she suspects Cruella will strike again despite her growing popularity as an animal person. Dipstick's mate, Dottie, gives birth to three puppies: Domino, Little Dipper, and Oddball, who appears to be an albino , and begins to feel self-conscious about her lack of spots as she grows up. Meanwhile, Dr. Pavlov discovers that when his therapy patients are subjected to the chimes of Big Ben , they revert to their former personalities, but he conceals these findings from the public. Inevitably, when Big Ben rings in her presence, Cruella reverts to her former personality. After recognizing Dipstick and remembering her failed attempt of making a dalmatian fur coat, she enlists the help of French furrier Jean-Pierre LePelt. Together, they design a new fur coat, with the intention of using Dipstick's children for a hood as a part of Cruella's revenge. Chloe and Kevin go out on a date, where Kevin tells Chloe that, if Cruella violates her parole, her entire fortune will go to him, since his dog shelter is the only one currently operating in Westminster. Knowing this, Cruella has Kevin framed for the theft of the first 99 dalmatian puppies LePelt takes, also exploiting the fact that Kevin has a prior record of dog-napping. She invites Chloe and Dipstick to her house for a dinner party to decoy them away while LePelt steals Dottie and her three puppies. Dipstick quickly returns to the apartment but is later captured. Chloe rushes home to save her pets but arrives too late. She is joined by Kevin, who has escaped from prison with the help of his talking macaw , Waddlesworth. Kevin explains that his earlier conviction was for breaking animals out of a lab, where they were being used for experiments . Upon finding LePelt's lost ticket for the Venice Simplon-Orient-Express to Paris , Kevin and Chloe attempt but fail to stop Cruella and LePelt before their train departs. Waddlesworth and Oddball, who managed to escape, secretly follow them to LePelt's factory in Paris. Kevin and Chloe get there as well but they are discovered by Cruella, who locks them in a cellar. Despite this, they free the puppies through a hole in the ceiling. Cruella goes after the puppies alone, while Alonzo, having been mistreated beyond his patience, defeats LePelt and frees Kevin and Chloe. They pursue Cruella to a bakery and find that the puppies, led by Oddball, have tricked Cruella into being baked in an enormous cake. Cruella survives, then she and LePelt are both arrested. Chloe and Kevin, exonerated from the theft accusation, return to London and are personally awarded the remnants of Cruella's fortune by Alonzo himself. Oddball's coat finally develops a few small spots, much to everyone's surprise.</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>November 13, 2000 ( 2000-11-13 ) ( Radio City Music Hall ) November 22, 2000 ( 2000-11-22 ) (United States)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>tt0211181</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>102_dalmatians_poster.jpg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>three year prison follow event previou film cruella de vil cure desir fur coat psychologist dr pavlov becom chang woman releas probat warn break parol immedi sent back prison well forc pay remaind fortun 8 million dog shelter westminst cruella mend work relationship muchabus valet alonzo buy second chanc dog shelter own kevin shepherd save insolv cruella probat offic chloe simon owner dipstick one origin 101 dalmatian cruella stolen suspect cruella strike despit grow popular anim person dipstick mate dotti give birth three puppi domino littl dipper oddbal appear albino begin feel selfconsci lack spot grow meanwhil dr pavlov discov therapi patient subject chime big ben revert former person conceal find public inevit big ben ring presenc cruella revert former person recogn dipstick rememb fail attempt make dalmatian fur coat enlist help french furrier jeanpierr lepelt togeth design new fur coat intent use dipstick child hood part cruella reveng chloe kevin go date kevin tell chloe cruella violat parol entir fortun go sinc dog shelter one current oper westminst know cruella kevin frame theft first 99 dalmatian puppi lepelt take also exploit fact kevin prior record dognap invit chloe dipstick hous dinner parti decoy away lepelt steal dotti three puppi dipstick quickli return apart later captur chloe rush home save pet arriv late join kevin escap prison help talk macaw waddlesworth kevin explain earlier convict break anim lab use experi upon find lepelt lost ticket venic simplonorientexpress pari kevin chloe attempt fail stop cruella lepelt train depart waddlesworth oddbal manag escap secretli follow lepelt factori pari kevin chloe get well discov cruella lock cellar despit free puppi hole ceil cruella goe puppi alon alonzo mistreat beyond patienc defeat lepelt free kevin chloe pursu cruella bakeri find puppi led oddbal trick cruella bake enorm cake cruella surviv lepelt arrest chloe kevin exoner theft accus return london person award remnant cruella fortun alonzo oddbal coat final develop small spot much everyon surpris</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>kevin lima</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>['glenn close', 'ioan gruffudd', 'alice evans', 'tim mcinnerny', 'gérard depardieu']</t>
-        </is>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>17</v>
+      </c>
+      <c r="I2" t="s">
+        <v>18</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>20</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>101 Dalmatians(1996 film)</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Stephen Herek</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Glenn Close, Jeff Daniels, Joely Richardson, Joan Plowright</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>American video game designer Roger Dearly lives with his pet Dalmatian Pongo in London. Roger develops a video game featuring dog chase, but it is rejected because the villain is inadequate. His attempts to redesign the game prove unsatisfactory. One day during a walk, Pongo sets his eyes on Perdita, another Dalmatian. After a chase that ends in St James's Park , Roger discovers that Pongo likes Perdita. Her owner, Anita Campbell-Green, falls in love with Roger when they meet. When they return to Roger's home, Anita accepts his proposal. They get married along with Perdita and Pongo. Anita works as a fashion designer at the House of de Vil. Her boss, Cruella de Vil , has a deep passion for fur, going so far as to have a taxidermist , Mr. Skinner, skin a white tiger at the London Zoo to make her into a rug for her. Anita, inspired by her Dalmatian, designs a coat made with spotted fur. Cruella is intrigued by the idea of making garments out of actual Dalmatians, and finds it amusing that it would seem as if she was wearing Anita's dog. Perdita gets pregnant, and so does Anita. Cruella visits their home and becomes excited when she learns that Perdita is expecting. Weeks later, she returns when a litter of 15 puppies are born and offers Roger and Anita £7,500 for them, but they refuse. Enraged, Cruella dismisses Anita and vows revenge against her and Roger. One winter evening, she has her henchmen, Jasper and Horace, break into their home and steal the puppies, while the couple is walking in the park with Pongo and Perdita. Along with 84 other Dalmatians that were previously stolen, they deliver them to her broken-down country estate , De Vil Mansion. Cruella asks Skinner to kill and skin them to create her coat. With the family devastated at the loss of their puppies, Pongo uses the twilight bark to carry the message via the dogs and other animals of the United Kingdom, while Roger and Anita notify the police . Anita realizes Cruella was behind the kidnappings and confirms her suspicion when she shows Roger and Nanny her portfolio. An Airedale Terrier named Kipper follows Jasper and Horace to the mansion, and finds all of the puppies, who he helps escape under the duo's noses. They make their way to a nearby farm, where they are later joined by Pongo and Perdita. Cruella arrives at the mansion and discovers what has happened. Angry with the thieves' failure, she decides to carry out the job herself. After several mishaps, Jasper and Horace discover nearby police looking for Cruella and hand themselves in, joining Skinner who was attacked in defense while trying to capture a puppy who had been left behind. Cruella tracks the puppies to the farm and tries to capture them, but the farm animals incapacitate her. The police arrive and arrest Cruella, before sending the puppies home. Pongo, Perdita and their puppies are reunited with Roger, Anita and Nanny. After being informed that the remaining 84 puppies have no home to go to, as they have not yet been claimed by any owners, they decide to adopt them. Roger finally creates a successful redesign his video game, featuring Dalmatian puppies as the protagonists and Cruella as the villain. With this success, they move out of London to the countryside with their millions. Roger and Anita have a baby girl, while the dogs grow up with puppies of their own.</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>November 18, 1996 ( 1996-11-18 ) ( Radio City Music Hall ) November 27, 1996 ( 1996-11-27 ) (United States)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>tt0115433</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>One_hundred_and_one_dalmatians_ver2.jpg</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>american video game design roger dearli live pet dalmatian pongo london roger develop video game featur dog chase reject villain inadequ attempt redesign game prove unsatisfactori one day walk pongo set eye perdita anoth dalmatian chase end st james park roger discov pongo like perdita owner anita campbellgreen fall love roger meet return roger home anita accept propos get marri along perdita pongo anita work fashion design hous de vil bos cruella de vil deep passion fur go far taxidermist mr skinner skin white tiger london zoo make rug anita inspir dalmatian design coat made spot fur cruella intrigu idea make garment actual dalmatian find amus would seem wear anita dog perdita get pregnant anita cruella visit home becom excit learn perdita expect week later return litter 15 puppi born offer roger anita 7500 refus enrag cruella dismiss anita vow reveng roger one winter even henchman jasper horac break home steal puppi coupl walk park pongo perdita along 84 dalmatian previous stolen deliv brokendown countri estat de vil mansion cruella ask skinner kill skin creat coat famili devast loss puppi pongo use twilight bark carri messag via dog anim unit kingdom roger anita notifi polic anita realiz cruella behind kidnap confirm suspicion show roger nanni portfolio airedal terrier name kipper follow jasper horac mansion find puppi help escap duo nose make way nearbi farm later join pongo perdita cruella arriv mansion discov happen angri thiev failur decid carri job sever mishap jasper horac discov nearbi polic look cruella hand join skinner attack defens tri captur puppi left behind cruella track puppi farm tri captur farm anim incapacit polic arriv arrest cruella send puppi home pongo perdita puppi reunit roger anita nanni inform remain 84 puppi home go yet claim owner decid adopt roger final creat success redesign video game featur dalmatian puppi protagonist cruella villain success move london countrysid million roger anita babi girl dog grow puppi</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>stephen herek</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>['glenn close', 'jeff daniels', 'joely richardson', 'joan plowright']</t>
-        </is>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" t="s">
+        <v>25</v>
+      </c>
+      <c r="G3" t="s">
+        <v>26</v>
+      </c>
+      <c r="H3" t="s">
+        <v>27</v>
+      </c>
+      <c r="I3" t="s">
+        <v>28</v>
+      </c>
+      <c r="J3" t="s">
+        <v>29</v>
+      </c>
+      <c r="K3" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
